--- a/Выплаты.xlsx
+++ b/Выплаты.xlsx
@@ -3,59 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FF502F-6328-9C43-BDC9-FE0F516BF5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE123E53-31CC-3B46-A49D-8070B63F2DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11260" yWindow="3360" windowWidth="21160" windowHeight="12440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11260" yWindow="3360" windowWidth="21160" windowHeight="12440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист2" sheetId="2" r:id="rId1"/>
-    <sheet name="Лист1" sheetId="3" r:id="rId2"/>
+    <sheet name="Лист1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>денежная выплата</t>
-  </si>
-  <si>
-    <t>оплата жилого помещения и коммунальных услуг</t>
-  </si>
-  <si>
-    <t>лекарственное обеспечение</t>
-  </si>
-  <si>
-    <t>инвалиды</t>
-  </si>
-  <si>
-    <t>труженики тыла</t>
-  </si>
-  <si>
-    <t>ветераны труда</t>
-  </si>
-  <si>
-    <t>пенсионеры, не относящиеся к льготным категориям</t>
-  </si>
-  <si>
-    <t>Категория</t>
-  </si>
-  <si>
-    <t>оплата и установка телефона</t>
-  </si>
-  <si>
-    <t>санаторно-курортное лечение</t>
-  </si>
-  <si>
-    <t>другие меры</t>
-  </si>
-  <si>
-    <t>ветераны Великой Отечественной Войны, кроме тружеников тыла</t>
-  </si>
-  <si>
-    <t>реабилитированные лица и лица, признанные пострадавшими от политических репрессий</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Денежная выплата</t>
   </si>
@@ -107,25 +67,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -148,19 +95,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -472,319 +413,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="72">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>248264</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>94437</v>
-      </c>
-      <c r="E2" s="3">
-        <v>10658774</v>
-      </c>
-      <c r="F2" s="3">
-        <v>266115</v>
-      </c>
-      <c r="G2" s="3">
-        <v>773567</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="24">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>66354</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1945714</v>
-      </c>
-      <c r="D3" s="3">
-        <v>16302</v>
-      </c>
-      <c r="E3" s="3">
-        <v>15000473</v>
-      </c>
-      <c r="F3" s="3">
-        <v>201083</v>
-      </c>
-      <c r="G3" s="3">
-        <v>910861</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>10591</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7785</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1582076</v>
-      </c>
-      <c r="F4" s="3">
-        <v>15314</v>
-      </c>
-      <c r="G4" s="3">
-        <v>706834</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3">
-        <v>37215</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1221996</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1295391</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
-        <v>5350</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1244451</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1317</v>
-      </c>
-      <c r="E6" s="3">
-        <v>777970</v>
-      </c>
-      <c r="F6" s="3">
-        <v>84995</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1025192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>4439605</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>173</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF966493-496F-4246-9763-652B2FDCFBA4}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="48">
-      <c r="A1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="5"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>248264</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>66354</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>37215</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>5350</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>1319</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1945714</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>1221996</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1244451</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>94437</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>16302</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>26115</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1317</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>10658774</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>15000473</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>5350</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>777970</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>266115</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>201083</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>84995</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>84995</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>773567</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>910861</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>1295391</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>1025192</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>3405603.3333333302</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>4420745.8</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>731088.2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>762961.99999999895</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>3805181.6190476199</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>4819969.0285714297</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>812777.11428571399</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>831461.85714285704</v>
       </c>
     </row>
